--- a/docs/review/劣化Sim_ツール評価結果_261013.xlsx
+++ b/docs/review/劣化Sim_ツール評価結果_261013.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -108,6 +108,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -769,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:G22"/>
+  <dimension ref="B3:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="7.5703125" customWidth="1" style="3" min="1" max="1"/>
@@ -1296,6 +1299,70 @@
       </c>
       <c r="G22" s="9" t="n"/>
     </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>■ 2026年10月14日時点の追加対応（担当者テストでの気づき・評価メモ対応）</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n"/>
+      <c r="D23" s="1" t="n"/>
+      <c r="E23" s="1" t="n"/>
+      <c r="F23" s="1" t="n"/>
+      <c r="G23" s="1" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="B24" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>④実行タブに、選択中ステップの動画情報（総フレーム数・fps・ACCEL_RATIO換算の1周回のAging時間・現在のAGING_TIME設定が無制限／打切り／周回のどれになるか＋見積りフレーム数）を表示する機能を追加。担当者の動作確認での要望への対応。</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>変更</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>堀部</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>対応済み (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="B25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>AGING_TIMEの挙動について確認：ACCEL_RATIOが大きい（既定30000）場合、1フレームあたりの加速込み時間が約1000秒規模になるため、AGING_TIMEが小さい値（例: 10秒・20秒）はどちらも「最低1フレームは処理する」ルールに丸められ、結果が区別できないことを確認（担当者の動作確認で気づいた現象。バグではなく、ACCEL_RATIOとAGING_TIMEの粒度関係による制約）。上記の見積りフレーム数表示で事前に確認できるようにした。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>堀部</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>確認済み (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
